--- a/docs/Test_Report/Fls/TestPlanExecutionReport_Fls.xlsx
+++ b/docs/Test_Report/Fls/TestPlanExecutionReport_Fls.xlsx
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 08:08:02.770464-05:00 CDT</t>
+          <t>2025-08-29 05:02:20.709212-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1582,7 +1582,39 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -1617,12 +1649,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1636,12 +1668,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1673,7 +1705,39 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -1708,12 +1772,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1727,12 +1791,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1764,7 +1828,39 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -1799,12 +1895,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1818,12 +1914,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1863,7 +1959,39 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1899,12 +2027,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -1918,12 +2046,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1963,7 +2091,39 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1999,12 +2159,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2018,12 +2178,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2063,7 +2223,39 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -2099,12 +2291,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2118,12 +2310,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2158,7 +2350,39 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -2194,12 +2418,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2213,12 +2437,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2250,7 +2474,39 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -2285,12 +2541,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2304,12 +2560,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2341,7 +2597,39 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -2376,12 +2664,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2395,12 +2683,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2432,7 +2720,39 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
@@ -2468,12 +2788,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2487,12 +2807,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2524,7 +2844,39 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -2559,12 +2911,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2578,12 +2930,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2615,7 +2967,39 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -2651,12 +3035,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -2670,12 +3054,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2712,7 +3096,39 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2748,12 +3164,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -2767,12 +3183,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2809,7 +3225,39 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2844,12 +3292,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -2863,12 +3311,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2903,7 +3351,39 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2939,12 +3419,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -2958,12 +3438,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2998,7 +3478,39 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -3033,12 +3545,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3052,12 +3564,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3089,7 +3601,39 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -3124,12 +3668,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3143,12 +3687,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3162,7 +3706,11 @@
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -3182,7 +3730,39 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -3218,12 +3798,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3237,12 +3817,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -3256,7 +3836,11 @@
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -3277,7 +3861,39 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -3313,12 +3929,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -3332,12 +3948,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -3351,7 +3967,11 @@
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -3372,7 +3992,39 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -3408,12 +4060,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -3427,12 +4079,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -3467,7 +4119,39 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -3502,12 +4186,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -3521,12 +4205,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -3561,7 +4245,39 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
@@ -3596,12 +4312,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -3615,12 +4331,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -3655,7 +4371,39 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -3690,12 +4438,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -3709,12 +4457,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -3749,7 +4497,39 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3784,12 +4564,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -3803,12 +4583,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -3841,7 +4621,39 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -3877,12 +4689,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -3896,12 +4708,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -3933,7 +4745,39 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -3969,12 +4813,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -3988,12 +4832,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4027,7 +4871,39 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -4062,12 +4938,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -4081,12 +4957,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -4121,7 +4997,39 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
@@ -4156,12 +5064,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -4175,12 +5083,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4217,7 +5125,39 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -4252,12 +5192,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -4271,12 +5211,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -4313,7 +5253,39 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -4348,12 +5320,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -4367,12 +5339,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -4404,7 +5376,39 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
@@ -4439,12 +5443,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -4458,12 +5462,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -4477,7 +5481,11 @@
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>No Associated Issues provided for the Test Case in Jira.</t>
+        </is>
+      </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -4495,7 +5503,39 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
@@ -4530,12 +5570,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -4549,12 +5589,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4586,7 +5626,39 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -4621,12 +5693,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -4640,12 +5712,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -4683,7 +5755,39 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -4718,12 +5822,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -4737,12 +5841,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -4780,7 +5884,39 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -4815,12 +5951,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -4834,12 +5970,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -4877,7 +6013,39 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
@@ -4912,12 +6080,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -4931,12 +6099,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -4968,7 +6136,39 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -5004,12 +6204,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -5023,12 +6223,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -5061,7 +6261,39 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
@@ -5097,12 +6329,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -5116,12 +6348,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -5153,7 +6385,39 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
@@ -5188,12 +6452,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -5207,12 +6471,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -5248,7 +6512,39 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -5283,12 +6579,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -5302,12 +6598,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -5342,7 +6638,39 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -5377,12 +6705,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -5396,12 +6724,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -5436,7 +6764,39 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
@@ -5471,12 +6831,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -5490,12 +6850,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -5532,7 +6892,39 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
@@ -5567,12 +6959,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -5586,12 +6978,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -5628,7 +7020,39 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -5663,12 +7087,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -5682,12 +7106,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -5724,7 +7148,39 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -5759,12 +7215,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -5778,12 +7234,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -5820,7 +7276,39 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -5855,12 +7343,12 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -5874,12 +7362,12 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -5916,7 +7404,39 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test2",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test2/Fls_UnitTest_02.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -5951,12 +7471,12 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
@@ -5970,12 +7490,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -6007,7 +7527,39 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
@@ -6043,12 +7595,12 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
@@ -6062,12 +7614,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -6099,7 +7651,39 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -6135,12 +7719,12 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
@@ -6154,12 +7738,12 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -6195,7 +7779,39 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
@@ -6230,12 +7846,12 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -6249,12 +7865,12 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -6289,7 +7905,39 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -6324,12 +7972,12 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
@@ -6343,12 +7991,12 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -6383,7 +8031,39 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
@@ -6418,12 +8098,12 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -6437,12 +8117,12 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -6478,7 +8158,39 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
@@ -6513,12 +8225,12 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
@@ -6532,12 +8244,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -6573,7 +8285,39 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -6608,12 +8352,12 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
@@ -6627,12 +8371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -6668,7 +8412,39 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -6703,12 +8479,12 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
@@ -6722,12 +8498,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -6763,7 +8539,39 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
@@ -6798,12 +8606,12 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -6817,12 +8625,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6858,7 +8666,39 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
@@ -6893,12 +8733,12 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
@@ -6912,12 +8752,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6950,7 +8790,39 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
@@ -6985,12 +8857,12 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
@@ -7004,12 +8876,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -7042,7 +8914,39 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
@@ -7077,12 +8981,12 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
@@ -7096,12 +9000,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -7136,7 +9040,39 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
@@ -7171,12 +9107,12 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
@@ -7190,12 +9126,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -7228,7 +9164,39 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
@@ -7263,12 +9231,12 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
@@ -7282,12 +9250,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -7322,7 +9290,39 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
@@ -7357,12 +9357,12 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
@@ -7376,12 +9376,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -7415,7 +9415,39 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
@@ -7450,12 +9482,12 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
@@ -7469,12 +9501,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -7507,7 +9539,39 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
@@ -7542,12 +9606,12 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
@@ -7561,12 +9625,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -7601,7 +9665,39 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K66" s="3" t="inlineStr">
@@ -7636,12 +9732,12 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
@@ -7655,12 +9751,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -7695,7 +9791,39 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
@@ -7730,12 +9858,12 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -7749,12 +9877,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -7789,7 +9917,39 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -7824,12 +9984,12 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
@@ -7843,12 +10003,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -7880,7 +10040,39 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -7915,12 +10107,12 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr"/>
@@ -7934,12 +10126,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -7966,14 +10158,46 @@
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>1.The function Fls_Cancel shall set the job result to MEMIF_JOB_CANCELED if the job result currently has the value 
+          <t>SWS_Fls_00033:The function Fls_Cancel shall set the job result to MEMIF_JOB_CANCELED if the job result currently has the value 
 MEMIF_JOB_PENDING. Otherwise the function Fls_Cancel shall leave the job 
 result unchanged.</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -8009,12 +10233,12 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr"/>
@@ -8028,12 +10252,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -8060,13 +10284,45 @@
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>1. If configured, the function Fls_Cancel shall call the error 
+          <t>SWS_Fls_00147: If configured, the function Fls_Cancel shall call the error 
 notification function to inform the caller about the cancellation of a job.</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
@@ -8102,12 +10358,12 @@
       </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr"/>
@@ -8121,12 +10377,12 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -8153,12 +10409,44 @@
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>1. The function Fls_Cancel shall be pre-compile time configurable On/Off by the configuration parameter FlsCancelApi.</t>
+          <t>SWS_Fls_00183: The function Fls_Cancel shall be pre-compile time configurable On/Off by the configuration parameter FlsCancelApi.</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -8193,12 +10481,12 @@
       </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr"/>
@@ -8212,12 +10500,12 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -8252,7 +10540,39 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
@@ -8287,12 +10607,12 @@
       </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr"/>
@@ -8306,12 +10626,12 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -8348,7 +10668,39 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
@@ -8383,12 +10735,12 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr"/>
@@ -8402,12 +10754,12 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -8444,7 +10796,39 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
@@ -8479,12 +10863,12 @@
       </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr"/>
@@ -8498,12 +10882,12 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -8540,7 +10924,39 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
@@ -8575,12 +10991,12 @@
       </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -8594,12 +11010,12 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -8609,7 +11025,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Fls_Write:  Fls_Write shall set the FLS module status to MEMIF_BUSY</t>
+          <t>Fls_Write:  Fls_Write shall set the job result to MEMIF_JOB_PENDING</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr"/>
@@ -8626,12 +11042,44 @@
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>1. After initiating the write job, the function Fls_Write shall set the job result to MEMIF_JOB_PENDING.</t>
+          <t>SWS_Fls_00333: After initiating the write job, the function Fls_Write shall set the job result to MEMIF_JOB_PENDING.</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K77" s="3" t="inlineStr">
@@ -8667,12 +11115,12 @@
       </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S77" s="3" t="inlineStr"/>
@@ -8686,12 +11134,12 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -8718,12 +11166,44 @@
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>1. After initiating the write job, the function Fls_Write shall set the FLS module status to MEMIF_BUSY.</t>
+          <t>SWS_Fls_00332: After initiating the write job, the function Fls_Write shall set the FLS module status to MEMIF_BUSY.</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K78" s="3" t="inlineStr">
@@ -8759,12 +11239,12 @@
       </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr"/>
@@ -8778,12 +11258,12 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -8819,7 +11299,39 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K79" s="3" t="inlineStr">
@@ -8855,12 +11367,12 @@
       </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr"/>
@@ -8874,12 +11386,12 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -8914,7 +11426,39 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -8950,12 +11494,12 @@
       </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr"/>
@@ -8969,12 +11513,12 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -9009,7 +11553,39 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
@@ -9045,12 +11621,12 @@
       </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr"/>
@@ -9064,12 +11640,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -9106,7 +11682,39 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
@@ -9142,12 +11750,12 @@
       </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R82" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S82" s="3" t="inlineStr"/>
@@ -9161,12 +11769,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -9203,7 +11811,39 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
@@ -9239,12 +11879,12 @@
       </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R83" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S83" s="3" t="inlineStr"/>
@@ -9258,12 +11898,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -9299,7 +11939,39 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
@@ -9334,12 +12006,12 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R84" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S84" s="3" t="inlineStr"/>
@@ -9353,12 +12025,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -9394,7 +12066,39 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr">
@@ -9429,12 +12133,12 @@
       </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S85" s="3" t="inlineStr"/>
@@ -9448,12 +12152,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -9489,7 +12193,39 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr">
@@ -9524,12 +12260,12 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R86" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S86" s="3" t="inlineStr"/>
@@ -9543,12 +12279,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -9575,13 +12311,45 @@
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>After initiating the erase job, the function Fls_Erase shall set 
+          <t>SWS_Fls_00329, SRS_Fls_12136: After initiating the erase job, the function Fls_Erase shall set 
 the job result to MEMIF_JOB_PENDING.</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
@@ -9616,12 +12384,12 @@
       </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
@@ -9635,12 +12403,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -9667,12 +12435,44 @@
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>After initiating the erase job, the function Fls_Erase shall set the FLS module status to MEMIF_BUSY.</t>
+          <t>SWS_Fls_00328: After initiating the erase job, the function Fls_Erase shall set the FLS module status to MEMIF_BUSY.</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -9707,12 +12507,12 @@
       </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
@@ -9726,12 +12526,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -9758,7 +12558,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>If development error detection for the module Fls is enabled: the 
+          <t>SWS_Fls_00065, SRS_BSW_00406, SRS_Fls_00311: If development error detection for the module Fls is enabled: the 
 function Fls_Erase shall check that the FLS module has been initialized. If this 
 check fails, the function Fls_Erase shall reject the erase request, raise the 
 development error FLS_E_UNINIT and return with E_NOT_OK.</t>
@@ -9766,7 +12566,39 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
@@ -9802,12 +12634,12 @@
       </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
@@ -9821,12 +12653,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -9853,7 +12685,7 @@
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>If development error detection for the module Fls is enabled: the 
+          <t>SWS_Fls_00383:SWS_Fls_00312, SRS_Fls_12143: If development error detection for the module Fls is enabled: the 
 function Fls_Erase shall check that the FLS module is currently not busy. If this 
 Specification of Flash Driver
 AUTOSAR CP Release 4.3.1
@@ -9865,7 +12697,39 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
@@ -9901,12 +12765,12 @@
       </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
@@ -9920,12 +12784,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -9952,17 +12816,45 @@
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>If development error detection for the module Fls is enabled: the 
-function Fls_Erase shall check that the erase length is greater than 0 and that the 
-erase end address (erase start address + length) is aligned to a flash sector 
-boundary and that it lies within the specified upper flash address boundary. If this 
-check fails, the function Fls_Erase shall reject the erase request, raise the 
+          <t>SWS_Fls_00021, SRS_Fls_00310, SRS_Fls_12159, SRS_Fls_12136: If development error detection for the module Fls is enabled: the function Fls_Erase shall check that the erase length is greater than 0 and that the erase end address (erase start address + length) is aligned to a flash sector boundary and that it lies within the specified upper flash address boundary. If this check fails, the function Fls_Erase shall reject the erase request, raise the 
 development error FLS_E_PARAM_LENGTH and return with E_NOT_OK.</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
@@ -9998,12 +12890,12 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S91" s="3" t="inlineStr"/>
@@ -10017,12 +12909,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -10049,12 +12941,44 @@
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>If development error detection for the module Fls is enabled: the function Fls_Erase shall check that the erase start address (FlsBaseAddress + TargetAddress) is aligned to a flash sector boundary and that it lies within the specified lower and upper flash address boundaries. If this check fails, the function Fls_Erase shall reject the erase request, raise the development error FLS_E_PARAM_ADDRESS and return with E_NOT_OK.</t>
+          <t>SWS_Fls_00020: If development error detection for the module Fls is enabled: the function Fls_Erase shall check that the erase start address (FlsBaseAddress + TargetAddress) is aligned to a flash sector boundary and that it lies within the specified lower and upper flash address boundaries. If this check fails, the function Fls_Erase shall reject the erase request, raise the development error FLS_E_PARAM_ADDRESS and return with E_NOT_OK.</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
@@ -10090,12 +13014,12 @@
       </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S92" s="3" t="inlineStr"/>
@@ -10109,12 +13033,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -10141,13 +13065,44 @@
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>The function Fls_Init shall initialize the FLS module (software) and all flash memory relevant registers (hardware) with parameters 
-provided in the given configuration set.</t>
+          <t>SRS_Fls_12132, SWS_Fls_00048: The function Fls_Init shall initialize the FLS module (software) and all flash memory relevant registers (hardware) with parameters provided in the given configuration set.</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
@@ -10183,12 +13138,12 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R93" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S93" s="3" t="inlineStr"/>
@@ -10202,12 +13157,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -10234,13 +13189,44 @@
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>The function Fls_Init shall initialize the FLS module (software) and all flash memory relevant registers (hardware) with parameters 
-provided in the given configuration set.</t>
+          <t>SWS_Fls_00014, SWS_Fls_00323, SWS_Fls_00324, SWS_Fls_00191, SWS_Fls_00086: The function Fls_Init shall initialize the FLS module (software) and all flash memory relevant registers (hardware) with parameters provided in the given configuration set.</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
@@ -10276,12 +13262,12 @@
       </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R94" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S94" s="3" t="inlineStr"/>
@@ -10295,12 +13281,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -10327,13 +13313,44 @@
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>The function Fls_Init shall initialize the FLS module (software) and all flash memory relevant registers (hardware) with parameters 
-provided in the given configuration set.</t>
+          <t>SWS_Fls_00249: The function Fls_Init shall initialize the FLS module (software) and all flash memory relevant registers (hardware) with parameters provided in the given configuration set.</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr">
@@ -10369,12 +13386,12 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S95" s="3" t="inlineStr"/>
@@ -10388,12 +13405,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -10420,14 +13437,46 @@
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>The function Fls_Init shall check that the FLS module is currently not busy (FLS 
+          <t>SWS_Fls_00268: The function Fls_Init shall check that the FLS module is currently not busy (FLS 
 module state is not MEMIF_BUSY). If this check fails, the function Fls_Init shall 
 raise the development error FLS_E_BUSY.</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
@@ -10462,12 +13511,12 @@
       </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R96" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S96" s="3" t="inlineStr"/>
@@ -10481,12 +13530,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30816</t>
+          <t>MCAL-32256</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : FLS - Manual Tests</t>
+          <t>C29xMCAL_01.03.00.00 : FLS - Manual Tests</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -10503,7 +13552,7 @@
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>F29H85x-evm</t>
+          <t>F29H85x-evm,F29P58x-evm</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -10513,14 +13562,46 @@
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>The function Fls_Init shall check the (hardware specific) contents of the given 
+          <t>[SWS_Fls_00015]: The function Fls_Init shall check the (hardware specific) contents of the given 
 Specification of Flash Driver
 configuration set for being within the allowed range. If this is not the case, it shall raise the development error FLS_E_PARAM_CONFIG.</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>{
+  "common_params": {
+    "core_os": [
+      "c29xx_cpu1"
+    ],
+    "test_app_name": "Fls_test1",
+    "scripts": "generic_mcu_json.py",
+    "no_of_cores": 1,
+    "skip_duplicate": "true",
+    "app_image": {
+      "image_1": {
+        "image_path": "f29h85x-evm/c29xx_cpu1/c29clang/ram/tests/Fls_test1/Fls_UnitTest_01.out"
+      }
+    },
+   "uart_input": {
+            "uart_input_1": {
+                "constraint": "Enter Choice:",
+                "timeout": 30,
+                "message": "Enter Choice successful",
+                "depends_prev": "false",
+                "port": "mcu0",
+                "send_command_with_newline": 1,
+                "command": "4"
+            }
+     },
+    "constraint": {
+      "constraint_1":{
+        "message": "All tests have passed",
+        "port": "mcu0"
+      }
+    }
+  }
+}</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
@@ -10555,12 +13636,12 @@
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30820</t>
+          <t>MCAL-32257</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01 : Fls - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00 : Fls - Manual Tests</t>
         </is>
       </c>
       <c r="S97" s="3" t="inlineStr"/>
